--- a/sulamericana/datasets_sula/1_confrontos_oitavas_sula.xlsx
+++ b/sulamericana/datasets_sula/1_confrontos_oitavas_sula.xlsx
@@ -112,52 +112,52 @@
     <t>2_8</t>
   </si>
   <si>
-    <t>SUPER VASCÃO F.C</t>
-  </si>
-  <si>
-    <t>FBC Colorado</t>
-  </si>
-  <si>
-    <t>Gig@ntte</t>
+    <t>JUV. KP</t>
+  </si>
+  <si>
+    <t>Máquina Laranjja</t>
+  </si>
+  <si>
+    <t>dasdoresfc</t>
+  </si>
+  <si>
+    <t>Grêmio imortal 36</t>
+  </si>
+  <si>
+    <t>FÚRIA LEON</t>
+  </si>
+  <si>
+    <t>AZURRA82</t>
+  </si>
+  <si>
+    <t>Grêmio imortal 37</t>
+  </si>
+  <si>
+    <t>Super Vasco f.c</t>
   </si>
   <si>
     <t>KillerColorado</t>
   </si>
   <si>
-    <t>Dom Camillo68</t>
-  </si>
-  <si>
-    <t>Noah A 10</t>
-  </si>
-  <si>
-    <t>KING LEONN</t>
-  </si>
-  <si>
-    <t>TEAM LOPES 99</t>
-  </si>
-  <si>
-    <t>FC Los Castilho</t>
+    <t>DM Studio</t>
+  </si>
+  <si>
+    <t>Tatols Beants F.C</t>
+  </si>
+  <si>
+    <t>JV5 Tricolor Gaúcho</t>
+  </si>
+  <si>
+    <t>Texas Club 2026</t>
+  </si>
+  <si>
+    <t>TORRESMO COM PINGA PRO26.1</t>
   </si>
   <si>
     <t>A Lenda Super Vasco F.c</t>
   </si>
   <si>
-    <t>Real SCI</t>
-  </si>
-  <si>
-    <t>Tatols Beants F.C</t>
-  </si>
-  <si>
-    <t>Paulo Virgili FC</t>
-  </si>
-  <si>
-    <t>MauHumor F.C.</t>
-  </si>
-  <si>
-    <t>seralex</t>
-  </si>
-  <si>
-    <t>lsauer fc</t>
+    <t>Mau Humor F.C.</t>
   </si>
 </sst>
 </file>
@@ -561,13 +561,13 @@
         <v>32</v>
       </c>
       <c r="F2">
-        <v>4229593</v>
+        <v>13951133</v>
       </c>
       <c r="G2" t="s">
         <v>40</v>
       </c>
       <c r="H2">
-        <v>25311459</v>
+        <v>36359</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -587,13 +587,13 @@
         <v>33</v>
       </c>
       <c r="F3">
-        <v>186283</v>
+        <v>30267301</v>
       </c>
       <c r="G3" t="s">
         <v>41</v>
       </c>
       <c r="H3">
-        <v>117598</v>
+        <v>387186</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -613,13 +613,13 @@
         <v>34</v>
       </c>
       <c r="F4">
-        <v>18421230</v>
+        <v>7017989</v>
       </c>
       <c r="G4" t="s">
         <v>42</v>
       </c>
       <c r="H4">
-        <v>3246608</v>
+        <v>212042</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -639,13 +639,13 @@
         <v>35</v>
       </c>
       <c r="F5">
-        <v>36359</v>
+        <v>24856400</v>
       </c>
       <c r="G5" t="s">
         <v>43</v>
       </c>
       <c r="H5">
-        <v>212042</v>
+        <v>1747619</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -665,13 +665,13 @@
         <v>36</v>
       </c>
       <c r="F6">
-        <v>20696550</v>
+        <v>18344271</v>
       </c>
       <c r="G6" t="s">
         <v>44</v>
       </c>
       <c r="H6">
-        <v>14124559</v>
+        <v>1273719</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -691,13 +691,13 @@
         <v>37</v>
       </c>
       <c r="F7">
-        <v>49960687</v>
+        <v>18346776</v>
       </c>
       <c r="G7" t="s">
         <v>45</v>
       </c>
       <c r="H7">
-        <v>25751748</v>
+        <v>47544767</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -717,13 +717,13 @@
         <v>38</v>
       </c>
       <c r="F8">
-        <v>13951133</v>
+        <v>24468241</v>
       </c>
       <c r="G8" t="s">
         <v>46</v>
       </c>
       <c r="H8">
-        <v>29228373</v>
+        <v>117598</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -743,13 +743,13 @@
         <v>39</v>
       </c>
       <c r="F9">
-        <v>479510</v>
+        <v>13707047</v>
       </c>
       <c r="G9" t="s">
         <v>47</v>
       </c>
       <c r="H9">
-        <v>44810918</v>
+        <v>19033717</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -769,13 +769,13 @@
         <v>40</v>
       </c>
       <c r="F10">
-        <v>25311459</v>
+        <v>36359</v>
       </c>
       <c r="G10" t="s">
         <v>32</v>
       </c>
       <c r="H10">
-        <v>4229593</v>
+        <v>13951133</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -795,13 +795,13 @@
         <v>41</v>
       </c>
       <c r="F11">
-        <v>117598</v>
+        <v>387186</v>
       </c>
       <c r="G11" t="s">
         <v>33</v>
       </c>
       <c r="H11">
-        <v>186283</v>
+        <v>30267301</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -821,13 +821,13 @@
         <v>42</v>
       </c>
       <c r="F12">
-        <v>3246608</v>
+        <v>212042</v>
       </c>
       <c r="G12" t="s">
         <v>34</v>
       </c>
       <c r="H12">
-        <v>18421230</v>
+        <v>7017989</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -847,13 +847,13 @@
         <v>43</v>
       </c>
       <c r="F13">
-        <v>212042</v>
+        <v>1747619</v>
       </c>
       <c r="G13" t="s">
         <v>35</v>
       </c>
       <c r="H13">
-        <v>36359</v>
+        <v>24856400</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -873,13 +873,13 @@
         <v>44</v>
       </c>
       <c r="F14">
-        <v>14124559</v>
+        <v>1273719</v>
       </c>
       <c r="G14" t="s">
         <v>36</v>
       </c>
       <c r="H14">
-        <v>20696550</v>
+        <v>18344271</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -899,13 +899,13 @@
         <v>45</v>
       </c>
       <c r="F15">
-        <v>25751748</v>
+        <v>47544767</v>
       </c>
       <c r="G15" t="s">
         <v>37</v>
       </c>
       <c r="H15">
-        <v>49960687</v>
+        <v>18346776</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -925,13 +925,13 @@
         <v>46</v>
       </c>
       <c r="F16">
-        <v>29228373</v>
+        <v>117598</v>
       </c>
       <c r="G16" t="s">
         <v>38</v>
       </c>
       <c r="H16">
-        <v>13951133</v>
+        <v>24468241</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -951,13 +951,13 @@
         <v>47</v>
       </c>
       <c r="F17">
-        <v>44810918</v>
+        <v>19033717</v>
       </c>
       <c r="G17" t="s">
         <v>39</v>
       </c>
       <c r="H17">
-        <v>479510</v>
+        <v>13707047</v>
       </c>
     </row>
   </sheetData>
